--- a/output/Tables/2019/cases_prev_2019.xlsx
+++ b/output/Tables/2019/cases_prev_2019.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -422,96 +422,109 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bc</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B4">
-        <v>3629.613692065931</v>
+        <v>4876.793711644698</v>
       </c>
       <c r="C4">
-        <v>276.4774555870436</v>
+        <v>354.3190521375493</v>
       </c>
       <c r="D4">
-        <v>4578.371663237075</v>
+        <v>107.3975247730567</v>
       </c>
       <c r="E4">
-        <v>1987.566796274164</v>
+        <v>9856.358715161285</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B5">
-        <v>4876.793711644698</v>
+        <v>6460.558313487762</v>
       </c>
       <c r="C5">
-        <v>354.3190521375493</v>
+        <v>474.1227074562376</v>
       </c>
       <c r="D5">
-        <v>107.3975247730567</v>
+        <v>-112.1764647045442</v>
       </c>
       <c r="E5">
-        <v>9856.358715161285</v>
+        <v>11942.14326808292</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B6">
-        <v>6460.558313487762</v>
+        <v>3575.150414314957</v>
       </c>
       <c r="C6">
-        <v>474.1227074562376</v>
+        <v>425.5825377946125</v>
       </c>
       <c r="D6">
-        <v>-112.1764647045442</v>
+        <v>2577.1836566209</v>
       </c>
       <c r="E6">
-        <v>11942.14326808292</v>
+        <v>4467.6733799249</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B7">
-        <v>3575.150414314957</v>
+        <v>178376.946648209</v>
       </c>
       <c r="C7">
-        <v>425.5825377946125</v>
+        <v>12254.94766055534</v>
       </c>
       <c r="D7">
-        <v>2577.1836566209</v>
+        <v>132879.5707832988</v>
       </c>
       <c r="E7">
-        <v>4467.6733799249</v>
+        <v>215571.340787943</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>Morbidity</t>
         </is>
       </c>
       <c r="B8">
-        <v>178376.946648209</v>
-      </c>
-      <c r="C8">
-        <v>12254.94766055534</v>
+        <v>203824.8670599548</v>
       </c>
       <c r="D8">
-        <v>132879.5707832988</v>
+        <v>142137.9311845388</v>
       </c>
       <c r="E8">
-        <v>215571.340787943</v>
+        <v>256088.7465297019</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>241482.2571816211</v>
+      </c>
+      <c r="D9">
+        <v>174034.0044714801</v>
+      </c>
+      <c r="E9">
+        <v>299103.3727228036</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/cases_prev_2019.xlsx
+++ b/output/Tables/2019/cases_prev_2019.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,22 +362,62 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>tot_cases</t>
+          <t>tot_cases_mid</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>tot_cases_se</t>
+          <t>tot_cases_low</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>tot_cases_low</t>
+          <t>tot_cases_up</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>tot_cases_up</t>
+          <t>tot_daly_mid</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_up</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_mid</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_up</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_mid</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_up</t>
         </is>
       </c>
     </row>
@@ -391,140 +431,295 @@
         <v>37657.39012166632</v>
       </c>
       <c r="C2">
-        <v>3405.72998118407</v>
+        <v>31896.07328694126</v>
       </c>
       <c r="D2">
-        <v>31896.07328694126</v>
+        <v>43014.62619310167</v>
       </c>
       <c r="E2">
-        <v>43014.62619310167</v>
+        <v>57548.24344989771</v>
+      </c>
+      <c r="F2">
+        <v>48888.35520242865</v>
+      </c>
+      <c r="G2">
+        <v>65606.61278759198</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>7653916378.836395</v>
+      </c>
+      <c r="L2">
+        <v>6502151241.923011</v>
+      </c>
+      <c r="M2">
+        <v>8725679500.749733</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cvd</t>
+          <t>bc</t>
         </is>
       </c>
       <c r="B3">
-        <v>10535.41797229838</v>
+        <v>777.3906568769762</v>
       </c>
       <c r="C3">
-        <v>830.7776885630304</v>
+        <v>22.40175943121739</v>
       </c>
       <c r="D3">
-        <v>6685.955684550638</v>
+        <v>1572.856985505977</v>
       </c>
       <c r="E3">
-        <v>14251.2303785898</v>
+        <v>205.4227740551028</v>
+      </c>
+      <c r="F3">
+        <v>3.840993288977415</v>
+      </c>
+      <c r="G3">
+        <v>525.5795513595959</v>
+      </c>
+      <c r="H3">
+        <v>34272821.88973517</v>
+      </c>
+      <c r="I3">
+        <v>987626.368044079</v>
+      </c>
+      <c r="J3">
+        <v>69342545.92000191</v>
+      </c>
+      <c r="K3">
+        <v>27321228.94932868</v>
+      </c>
+      <c r="L3">
+        <v>510852.1074339962</v>
+      </c>
+      <c r="M3">
+        <v>69902080.33082625</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>cvd</t>
         </is>
       </c>
       <c r="B4">
-        <v>4876.793711644698</v>
+        <v>10535.41797229838</v>
       </c>
       <c r="C4">
-        <v>354.3190521375493</v>
+        <v>6685.955684550638</v>
       </c>
       <c r="D4">
-        <v>107.3975247730567</v>
+        <v>14251.2303785898</v>
       </c>
       <c r="E4">
-        <v>9856.358715161285</v>
+        <v>1525.323511210987</v>
+      </c>
+      <c r="F4">
+        <v>762.377143976183</v>
+      </c>
+      <c r="G4">
+        <v>2507.825543887818</v>
+      </c>
+      <c r="H4">
+        <v>586843851.8929631</v>
+      </c>
+      <c r="I4">
+        <v>372421103.5408387</v>
+      </c>
+      <c r="J4">
+        <v>793822034.548208</v>
+      </c>
+      <c r="K4">
+        <v>202868026.9910612</v>
+      </c>
+      <c r="L4">
+        <v>101396160.1488323</v>
+      </c>
+      <c r="M4">
+        <v>333540797.3370798</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B5">
-        <v>6460.558313487762</v>
+        <v>4876.793711644698</v>
       </c>
       <c r="C5">
-        <v>474.1227074562376</v>
+        <v>107.3975247730567</v>
       </c>
       <c r="D5">
-        <v>-112.1764647045442</v>
+        <v>9856.358715161285</v>
       </c>
       <c r="E5">
-        <v>11942.14326808292</v>
+        <v>792.9264229528994</v>
+      </c>
+      <c r="F5">
+        <v>12.20139831412728</v>
+      </c>
+      <c r="G5">
+        <v>1850.477664960846</v>
+      </c>
+      <c r="H5">
+        <v>72210684.48832309</v>
+      </c>
+      <c r="I5">
+        <v>1590235.149314657</v>
+      </c>
+      <c r="J5">
+        <v>145943103.4953932</v>
+      </c>
+      <c r="K5">
+        <v>105459214.2527356</v>
+      </c>
+      <c r="L5">
+        <v>1622785.975778928</v>
+      </c>
+      <c r="M5">
+        <v>246113529.4397925</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B6">
-        <v>3575.150414314957</v>
+        <v>6460.558313487762</v>
       </c>
       <c r="C6">
-        <v>425.5825377946125</v>
+        <v>-112.1764647045442</v>
       </c>
       <c r="D6">
-        <v>2577.1836566209</v>
+        <v>11942.14326808292</v>
       </c>
       <c r="E6">
-        <v>4467.6733799249</v>
+        <v>1495.945257286311</v>
+      </c>
+      <c r="F6">
+        <v>-19.4054783622427</v>
+      </c>
+      <c r="G6">
+        <v>3511.60674925197</v>
+      </c>
+      <c r="H6">
+        <v>485840445.7325924</v>
+      </c>
+      <c r="I6">
+        <v>-8435782.322246449</v>
+      </c>
+      <c r="J6">
+        <v>898061115.9031025</v>
+      </c>
+      <c r="K6">
+        <v>198960719.2190793</v>
+      </c>
+      <c r="L6">
+        <v>-2580928.62217828</v>
+      </c>
+      <c r="M6">
+        <v>467043697.650512</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dep</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B7">
-        <v>178376.946648209</v>
+        <v>3575.150414314957</v>
       </c>
       <c r="C7">
-        <v>12254.94766055534</v>
+        <v>2577.1836566209</v>
       </c>
       <c r="D7">
-        <v>132879.5707832988</v>
+        <v>4467.6733799249</v>
       </c>
       <c r="E7">
-        <v>215571.340787943</v>
+        <v>795.1440854321614</v>
+      </c>
+      <c r="F7">
+        <v>460.4035855520572</v>
+      </c>
+      <c r="G7">
+        <v>1129.581374267413</v>
+      </c>
+      <c r="H7">
+        <v>60201957.82664964</v>
+      </c>
+      <c r="I7">
+        <v>43397195.59383941</v>
+      </c>
+      <c r="J7">
+        <v>75231152.04455553</v>
+      </c>
+      <c r="K7">
+        <v>105754163.3624775</v>
+      </c>
+      <c r="L7">
+        <v>61233676.8784236</v>
+      </c>
+      <c r="M7">
+        <v>150234322.777566</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Morbidity</t>
+          <t>dep</t>
         </is>
       </c>
       <c r="B8">
-        <v>203824.8670599548</v>
+        <v>178376.946648209</v>
+      </c>
+      <c r="C8">
+        <v>132879.5707832988</v>
       </c>
       <c r="D8">
-        <v>142137.9311845388</v>
+        <v>215571.340787943</v>
       </c>
       <c r="E8">
-        <v>256088.7465297019</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>241482.2571816211</v>
-      </c>
-      <c r="D9">
-        <v>174034.0044714801</v>
-      </c>
-      <c r="E9">
-        <v>299103.3727228036</v>
+        <v>196048.2217129566</v>
+      </c>
+      <c r="F8">
+        <v>90274.07537014296</v>
+      </c>
+      <c r="G8">
+        <v>362136.3274526611</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>26074413487.82323</v>
+      </c>
+      <c r="L8">
+        <v>12006452024.22901</v>
+      </c>
+      <c r="M8">
+        <v>48164131551.20393</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/cases_prev_2019.xlsx
+++ b/output/Tables/2019/cases_prev_2019.xlsx
@@ -471,40 +471,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>777.3906568769762</v>
+        <v>830.3701511487852</v>
       </c>
       <c r="C3">
-        <v>22.40175943121739</v>
+        <v>23.96606678829604</v>
       </c>
       <c r="D3">
-        <v>1572.856985505977</v>
+        <v>1679.989000054051</v>
       </c>
       <c r="E3">
-        <v>205.4227740551028</v>
+        <v>218.1251200341125</v>
       </c>
       <c r="F3">
-        <v>3.840993288977415</v>
+        <v>4.107719637279583</v>
       </c>
       <c r="G3">
-        <v>525.5795513595959</v>
+        <v>558.0467703075753</v>
       </c>
       <c r="H3">
-        <v>34272821.88973517</v>
+        <v>36608528.85369654</v>
       </c>
       <c r="I3">
-        <v>987626.368044079</v>
+        <v>1056591.986495604</v>
       </c>
       <c r="J3">
-        <v>69342545.92000191</v>
+        <v>74065675.04538301</v>
       </c>
       <c r="K3">
-        <v>27321228.94932868</v>
+        <v>29010640.96453696</v>
       </c>
       <c r="L3">
-        <v>510852.1074339962</v>
+        <v>546326.7117581846</v>
       </c>
       <c r="M3">
-        <v>69902080.33082625</v>
+        <v>74220220.45090751</v>
       </c>
     </row>
     <row r="4">
@@ -514,40 +514,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>10535.41797229838</v>
+        <v>26221.37654333101</v>
       </c>
       <c r="C4">
-        <v>6685.955684550638</v>
+        <v>16615.3887282639</v>
       </c>
       <c r="D4">
-        <v>14251.2303785898</v>
+        <v>35499.55489233022</v>
       </c>
       <c r="E4">
-        <v>1525.323511210987</v>
+        <v>3532.139363166874</v>
       </c>
       <c r="F4">
-        <v>762.377143976183</v>
+        <v>1763.888323674077</v>
       </c>
       <c r="G4">
-        <v>2507.825543887818</v>
+        <v>5808.676308761635</v>
       </c>
       <c r="H4">
-        <v>586843851.8929631</v>
+        <v>1460583116.216622</v>
       </c>
       <c r="I4">
-        <v>372421103.5408387</v>
+        <v>925510382.9417554</v>
       </c>
       <c r="J4">
-        <v>793822034.548208</v>
+        <v>1977396206.612579</v>
       </c>
       <c r="K4">
-        <v>202868026.9910612</v>
+        <v>469774535.3011943</v>
       </c>
       <c r="L4">
-        <v>101396160.1488323</v>
+        <v>234597147.0486522</v>
       </c>
       <c r="M4">
-        <v>333540797.3370798</v>
+        <v>772553949.0652974</v>
       </c>
     </row>
     <row r="5">
@@ -557,40 +557,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>4876.793711644698</v>
+        <v>19889.27164397337</v>
       </c>
       <c r="C5">
-        <v>107.3975247730567</v>
+        <v>454.7784485705045</v>
       </c>
       <c r="D5">
-        <v>9856.358715161285</v>
+        <v>40200.39952095928</v>
       </c>
       <c r="E5">
-        <v>792.9264229528994</v>
+        <v>4673.412228552141</v>
       </c>
       <c r="F5">
-        <v>12.20139831412728</v>
+        <v>85.806142490601</v>
       </c>
       <c r="G5">
-        <v>1850.477664960846</v>
+        <v>10908.68692539043</v>
       </c>
       <c r="H5">
-        <v>72210684.48832309</v>
+        <v>294500445.2323143</v>
       </c>
       <c r="I5">
-        <v>1590235.149314657</v>
+        <v>6733904.487983459</v>
       </c>
       <c r="J5">
-        <v>145943103.4953932</v>
+        <v>595247315.7068446</v>
       </c>
       <c r="K5">
-        <v>105459214.2527356</v>
+        <v>621563826.3974347</v>
       </c>
       <c r="L5">
-        <v>1622785.975778928</v>
+        <v>11412216.95124993</v>
       </c>
       <c r="M5">
-        <v>246113529.4397925</v>
+        <v>1450855361.076927</v>
       </c>
     </row>
     <row r="6">
@@ -600,40 +600,40 @@
         </is>
       </c>
       <c r="B6">
-        <v>6460.558313487762</v>
+        <v>4152.350169913546</v>
       </c>
       <c r="C6">
-        <v>-112.1764647045442</v>
+        <v>-69.85908051408144</v>
       </c>
       <c r="D6">
-        <v>11942.14326808292</v>
+        <v>7670.444748038176</v>
       </c>
       <c r="E6">
-        <v>1495.945257286311</v>
+        <v>1283.83683297256</v>
       </c>
       <c r="F6">
-        <v>-19.4054783622427</v>
+        <v>-17.20944773516335</v>
       </c>
       <c r="G6">
-        <v>3511.60674925197</v>
+        <v>3016.990236883345</v>
       </c>
       <c r="H6">
-        <v>485840445.7325924</v>
+        <v>312260885.1276684</v>
       </c>
       <c r="I6">
-        <v>-8435782.322246449</v>
+        <v>-5253472.713739468</v>
       </c>
       <c r="J6">
-        <v>898061115.9031025</v>
+        <v>576825115.4972181</v>
       </c>
       <c r="K6">
-        <v>198960719.2190793</v>
+        <v>170750298.7853505</v>
       </c>
       <c r="L6">
-        <v>-2580928.62217828</v>
+        <v>-2288856.548776726</v>
       </c>
       <c r="M6">
-        <v>467043697.650512</v>
+        <v>401259701.5054849</v>
       </c>
     </row>
     <row r="7">
@@ -643,40 +643,40 @@
         </is>
       </c>
       <c r="B7">
-        <v>3575.150414314957</v>
+        <v>9342.78379257431</v>
       </c>
       <c r="C7">
-        <v>2577.1836566209</v>
+        <v>6737.583701711718</v>
       </c>
       <c r="D7">
-        <v>4467.6733799249</v>
+        <v>11669.99409904738</v>
       </c>
       <c r="E7">
-        <v>795.1440854321614</v>
+        <v>2251.147078006146</v>
       </c>
       <c r="F7">
-        <v>460.4035855520572</v>
+        <v>1304.589292206264</v>
       </c>
       <c r="G7">
-        <v>1129.581374267413</v>
+        <v>3194.720844848354</v>
       </c>
       <c r="H7">
-        <v>60201957.82664964</v>
+        <v>157323136.2831588</v>
       </c>
       <c r="I7">
-        <v>43397195.59383941</v>
+        <v>113454171.953124</v>
       </c>
       <c r="J7">
-        <v>75231152.04455553</v>
+        <v>196511030.6338589</v>
       </c>
       <c r="K7">
-        <v>105754163.3624775</v>
+        <v>299402561.3748175</v>
       </c>
       <c r="L7">
-        <v>61233676.8784236</v>
+        <v>173510375.8634331</v>
       </c>
       <c r="M7">
-        <v>150234322.777566</v>
+        <v>424897872.3648311</v>
       </c>
     </row>
     <row r="8">
@@ -686,22 +686,22 @@
         </is>
       </c>
       <c r="B8">
-        <v>178376.946648209</v>
+        <v>94906.03726744022</v>
       </c>
       <c r="C8">
-        <v>132879.5707832988</v>
+        <v>70672.80004663614</v>
       </c>
       <c r="D8">
-        <v>215571.340787943</v>
+        <v>114720.7071280039</v>
       </c>
       <c r="E8">
-        <v>196048.2217129566</v>
+        <v>85258.20082058886</v>
       </c>
       <c r="F8">
-        <v>90274.07537014296</v>
+        <v>39264.36344476037</v>
       </c>
       <c r="G8">
-        <v>362136.3274526611</v>
+        <v>157478.6640062529</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -713,13 +713,13 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>26074413487.82323</v>
+        <v>11339340709.13832</v>
       </c>
       <c r="L8">
-        <v>12006452024.22901</v>
+        <v>5222160338.153129</v>
       </c>
       <c r="M8">
-        <v>48164131551.20393</v>
+        <v>20944662312.83164</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/cases_prev_2019.xlsx
+++ b/output/Tables/2019/cases_prev_2019.xlsx
@@ -428,22 +428,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>51089.7202592129</v>
+        <v>58808.72854619536</v>
       </c>
       <c r="C2">
-        <v>44616.28080132468</v>
+        <v>50683.17835160439</v>
       </c>
       <c r="D2">
-        <v>57190.71456997752</v>
+        <v>66422.72611868204</v>
       </c>
       <c r="E2">
-        <v>91916.10081600182</v>
+        <v>101345.5352829164</v>
       </c>
       <c r="F2">
-        <v>79934.55527304369</v>
+        <v>87412.68655836632</v>
       </c>
       <c r="G2">
-        <v>103189.8712020132</v>
+        <v>114407.1291214319</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -455,13 +455,13 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>12224841408.52824</v>
+        <v>13478956192.62788</v>
       </c>
       <c r="L2">
-        <v>10631295851.31481</v>
+        <v>11625887312.26272</v>
       </c>
       <c r="M2">
-        <v>13724252869.86775</v>
+        <v>15216148173.15045</v>
       </c>
     </row>
     <row r="3">
@@ -471,40 +471,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>1056.137328627854</v>
+        <v>1248.612815553223</v>
       </c>
       <c r="C3">
-        <v>60.93005378622075</v>
+        <v>61.29332648930076</v>
       </c>
       <c r="D3">
-        <v>2137.570231094892</v>
+        <v>2528.160142138328</v>
       </c>
       <c r="E3">
-        <v>296.6374997337918</v>
+        <v>343.1225477244411</v>
       </c>
       <c r="F3">
-        <v>12.49731954080242</v>
+        <v>12.06727726724682</v>
       </c>
       <c r="G3">
-        <v>759.7616819675889</v>
+        <v>878.8530461058352</v>
       </c>
       <c r="H3">
-        <v>46561926.40721618</v>
+        <v>55047593.19929488</v>
       </c>
       <c r="I3">
-        <v>2686223.281273113</v>
+        <v>2702238.884933811</v>
       </c>
       <c r="J3">
-        <v>94239058.77828044</v>
+        <v>111458996.1864522</v>
       </c>
       <c r="K3">
-        <v>39452787.46459431</v>
+        <v>45635298.84735067</v>
       </c>
       <c r="L3">
-        <v>1662143.498926722</v>
+        <v>1604947.876543826</v>
       </c>
       <c r="M3">
-        <v>101048303.7016893</v>
+        <v>116887455.1320761</v>
       </c>
     </row>
     <row r="4">
@@ -514,40 +514,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>34308.54723231314</v>
+        <v>39658.26680417132</v>
       </c>
       <c r="C4">
-        <v>21969.30350430946</v>
+        <v>25131.72686794779</v>
       </c>
       <c r="D4">
-        <v>46520.89011063688</v>
+        <v>53975.06871654517</v>
       </c>
       <c r="E4">
-        <v>5058.128911224283</v>
+        <v>5712.877803263514</v>
       </c>
       <c r="F4">
-        <v>2531.060918786668</v>
+        <v>2842.267574289006</v>
       </c>
       <c r="G4">
-        <v>8373.908011549674</v>
+        <v>9468.976052063043</v>
       </c>
       <c r="H4">
-        <v>1911054697.934306</v>
+        <v>2209044777.525945</v>
       </c>
       <c r="I4">
-        <v>1223734143.797054</v>
+        <v>1399887449.998425</v>
       </c>
       <c r="J4">
-        <v>2591306620.942682</v>
+        <v>3006519277.649013</v>
       </c>
       <c r="K4">
-        <v>672731145.1928296</v>
+        <v>759812747.8340473</v>
       </c>
       <c r="L4">
-        <v>336631102.1986269</v>
+        <v>378021587.3804378</v>
       </c>
       <c r="M4">
-        <v>1113729765.536107</v>
+        <v>1259373814.924385</v>
       </c>
     </row>
     <row r="5">
@@ -557,40 +557,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>26741.46857147965</v>
+        <v>30550.63989096155</v>
       </c>
       <c r="C5">
-        <v>1399.120480689715</v>
+        <v>1406.091732024955</v>
       </c>
       <c r="D5">
-        <v>54096.1683247946</v>
+        <v>61810.71484846871</v>
       </c>
       <c r="E5">
-        <v>6687.71356151794</v>
+        <v>7584.558293438183</v>
       </c>
       <c r="F5">
-        <v>294.3444336675286</v>
+        <v>284.2369732675789</v>
       </c>
       <c r="G5">
-        <v>15629.62265149308</v>
+        <v>17722.83320185035</v>
       </c>
       <c r="H5">
-        <v>395960925.1378974</v>
+        <v>452363324.8654665</v>
       </c>
       <c r="I5">
-        <v>20716776.95757248</v>
+        <v>20820000.27609352</v>
       </c>
       <c r="J5">
-        <v>801001964.3852346</v>
+        <v>915231254.7612746</v>
       </c>
       <c r="K5">
-        <v>889465903.681886</v>
+        <v>1008746253.027278</v>
       </c>
       <c r="L5">
-        <v>39147809.67778131</v>
+        <v>37803517.444588</v>
       </c>
       <c r="M5">
-        <v>2078739812.648579</v>
+        <v>2357136815.846096</v>
       </c>
     </row>
     <row r="6">
@@ -600,40 +600,40 @@
         </is>
       </c>
       <c r="B6">
-        <v>5768.329251396385</v>
+        <v>6494.644935378301</v>
       </c>
       <c r="C6">
-        <v>-160.6913250398804</v>
+        <v>-169.2346162776211</v>
       </c>
       <c r="D6">
-        <v>10825.14839816942</v>
+        <v>12160.73353396925</v>
       </c>
       <c r="E6">
-        <v>1868.015528768264</v>
+        <v>2091.204030004019</v>
       </c>
       <c r="F6">
-        <v>-40.75297510862155</v>
+        <v>-42.47659965253237</v>
       </c>
       <c r="G6">
-        <v>4460.537076775554</v>
+        <v>4980.793696439016</v>
       </c>
       <c r="H6">
-        <v>433784128.0342588</v>
+        <v>488403793.7853814</v>
       </c>
       <c r="I6">
-        <v>-12084148.33432404</v>
+        <v>-12726612.37869336</v>
       </c>
       <c r="J6">
-        <v>814061984.690743</v>
+        <v>914499322.4880207</v>
       </c>
       <c r="K6">
-        <v>248446065.3261791</v>
+        <v>278130135.9905345</v>
       </c>
       <c r="L6">
-        <v>-5420145.689446666</v>
+        <v>-5649387.753786805</v>
       </c>
       <c r="M6">
-        <v>593251431.2111486</v>
+        <v>662445561.626389</v>
       </c>
     </row>
     <row r="7">
@@ -643,40 +643,40 @@
         </is>
       </c>
       <c r="B7">
-        <v>11218.11869998985</v>
+        <v>13489.4385254247</v>
       </c>
       <c r="C7">
-        <v>8258.840936625313</v>
+        <v>9828.706059099071</v>
       </c>
       <c r="D7">
-        <v>13880.15720498462</v>
+        <v>16781.06039131099</v>
       </c>
       <c r="E7">
-        <v>2947.713279831712</v>
+        <v>3448.375467569117</v>
       </c>
       <c r="F7">
-        <v>1735.92601824419</v>
+        <v>2016.282089170447</v>
       </c>
       <c r="G7">
-        <v>4157.269141919008</v>
+        <v>4879.598587488372</v>
       </c>
       <c r="H7">
-        <v>188901900.7891289</v>
+        <v>227148655.3296263</v>
       </c>
       <c r="I7">
-        <v>139070622.5318339</v>
+        <v>165505581.3291695</v>
       </c>
       <c r="J7">
-        <v>233727967.1747361</v>
+        <v>282576275.9292844</v>
       </c>
       <c r="K7">
-        <v>392045866.2176178</v>
+        <v>458633937.1866926</v>
       </c>
       <c r="L7">
-        <v>230878160.4264773</v>
+        <v>268165517.8596694</v>
       </c>
       <c r="M7">
-        <v>552916795.875228</v>
+        <v>648986612.1359534</v>
       </c>
     </row>
     <row r="8">
@@ -686,22 +686,22 @@
         </is>
       </c>
       <c r="B8">
-        <v>133534.2739406437</v>
+        <v>152108.7678282618</v>
       </c>
       <c r="C8">
-        <v>98618.17222058402</v>
+        <v>112504.7828238988</v>
       </c>
       <c r="D8">
-        <v>162095.770370954</v>
+        <v>184478.6729160412</v>
       </c>
       <c r="E8">
-        <v>127668.0348175325</v>
+        <v>143829.9205117502</v>
       </c>
       <c r="F8">
-        <v>58276.00831111365</v>
+        <v>65787.39343756315</v>
       </c>
       <c r="G8">
-        <v>236884.8784959097</v>
+        <v>266585.2675931788</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -713,13 +713,13 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>16979848630.73182</v>
+        <v>19129379428.06278</v>
       </c>
       <c r="L8">
-        <v>7750709105.378116</v>
+        <v>8749723327.1959</v>
       </c>
       <c r="M8">
-        <v>31505688839.95599</v>
+        <v>35455840589.89278</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/cases_prev_2019.xlsx
+++ b/output/Tables/2019/cases_prev_2019.xlsx
@@ -1,21 +1,89 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/2019/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E11EAC3-8B5D-7647-84DA-7477D18880B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="34040" yWindow="-940" windowWidth="19980" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>tot_cases_mid</t>
+  </si>
+  <si>
+    <t>tot_cases_low</t>
+  </si>
+  <si>
+    <t>tot_cases_up</t>
+  </si>
+  <si>
+    <t>tot_daly_mid</t>
+  </si>
+  <si>
+    <t>tot_daly_low</t>
+  </si>
+  <si>
+    <t>tot_daly_up</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_mid</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_low</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_up</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_mid</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_up</t>
+  </si>
+  <si>
+    <t>mort</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>cancer</t>
+  </si>
+  <si>
+    <t>diab2</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>dep</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +131,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +183,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +217,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +252,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,100 +428,85 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_mid</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_up</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_mid</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_up</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_mid</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_low</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_up</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_mid</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_up</t>
-        </is>
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>13</v>
       </c>
       <c r="B2">
-        <v>58808.72854619536</v>
+        <v>58808.728546195358</v>
       </c>
       <c r="C2">
-        <v>50683.17835160439</v>
+        <v>50683.178351604387</v>
       </c>
       <c r="D2">
         <v>66422.72611868204</v>
       </c>
       <c r="E2">
-        <v>101345.5352829164</v>
+        <v>608073.21169749764</v>
       </c>
       <c r="F2">
-        <v>87412.68655836632</v>
+        <v>524476.11935019644</v>
       </c>
       <c r="G2">
-        <v>114407.1291214319</v>
+        <v>686442.77472859167</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -455,271 +518,218 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>13478956192.62788</v>
+        <v>80873737155.767181</v>
       </c>
       <c r="L2">
-        <v>11625887312.26272</v>
+        <v>69755323873.576126</v>
       </c>
       <c r="M2">
-        <v>15216148173.15045</v>
+        <v>91296889038.902695</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>bc</t>
-        </is>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
       </c>
       <c r="B3">
-        <v>1248.612815553223</v>
+        <v>39658.266804171319</v>
       </c>
       <c r="C3">
-        <v>61.29332648930076</v>
+        <v>25131.726867947789</v>
       </c>
       <c r="D3">
-        <v>2528.160142138328</v>
+        <v>53975.068716545167</v>
       </c>
       <c r="E3">
-        <v>343.1225477244411</v>
+        <v>34277.266819580909</v>
       </c>
       <c r="F3">
-        <v>12.06727726724682</v>
+        <v>17053.605445734069</v>
       </c>
       <c r="G3">
-        <v>878.8530461058352</v>
+        <v>56813.856312378193</v>
       </c>
       <c r="H3">
-        <v>55047593.19929488</v>
+        <v>2209044777.5259452</v>
       </c>
       <c r="I3">
-        <v>2702238.884933811</v>
+        <v>1399887449.998425</v>
       </c>
       <c r="J3">
-        <v>111458996.1864522</v>
+        <v>3006519277.649013</v>
       </c>
       <c r="K3">
-        <v>45635298.84735067</v>
+        <v>4558876487.004261</v>
       </c>
       <c r="L3">
-        <v>1604947.876543826</v>
+        <v>2268129524.28263</v>
       </c>
       <c r="M3">
-        <v>116887455.1320761</v>
+        <v>7556242889.5462999</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>15</v>
       </c>
       <c r="B4">
-        <v>39658.26680417132</v>
+        <v>30550.639890961549</v>
       </c>
       <c r="C4">
-        <v>25131.72686794779</v>
+        <v>1406.091732024955</v>
       </c>
       <c r="D4">
-        <v>53975.06871654517</v>
+        <v>61810.714848468713</v>
       </c>
       <c r="E4">
-        <v>5712.877803263514</v>
+        <v>45507.349760629091</v>
       </c>
       <c r="F4">
-        <v>2842.267574289006</v>
+        <v>1705.4218396054689</v>
       </c>
       <c r="G4">
-        <v>9468.976052063043</v>
+        <v>106336.9992111021</v>
       </c>
       <c r="H4">
-        <v>2209044777.525945</v>
+        <v>452363324.86546648</v>
       </c>
       <c r="I4">
-        <v>1399887449.998425</v>
+        <v>20820000.27609352</v>
       </c>
       <c r="J4">
-        <v>3006519277.649013</v>
+        <v>915231254.76127458</v>
       </c>
       <c r="K4">
-        <v>759812747.8340473</v>
+        <v>6052477518.1636696</v>
       </c>
       <c r="L4">
-        <v>378021587.3804378</v>
+        <v>226821104.66752741</v>
       </c>
       <c r="M4">
-        <v>1259373814.924385</v>
+        <v>14142820895.07658</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>16</v>
       </c>
       <c r="B5">
-        <v>30550.63989096155</v>
+        <v>6494.6449353783009</v>
       </c>
       <c r="C5">
-        <v>1406.091732024955</v>
+        <v>-169.23461627762109</v>
       </c>
       <c r="D5">
-        <v>61810.71484846871</v>
+        <v>12160.733533969251</v>
       </c>
       <c r="E5">
-        <v>7584.558293438183</v>
+        <v>12547.224180024181</v>
       </c>
       <c r="F5">
-        <v>284.2369732675789</v>
+        <v>-254.85959791519619</v>
       </c>
       <c r="G5">
-        <v>17722.83320185035</v>
+        <v>29884.76217863405</v>
       </c>
       <c r="H5">
-        <v>452363324.8654665</v>
+        <v>488403793.78538138</v>
       </c>
       <c r="I5">
-        <v>20820000.27609352</v>
+        <v>-12726612.378693361</v>
       </c>
       <c r="J5">
-        <v>915231254.7612746</v>
+        <v>914499322.48802066</v>
       </c>
       <c r="K5">
-        <v>1008746253.027278</v>
+        <v>1668780815.9432149</v>
       </c>
       <c r="L5">
-        <v>37803517.444588</v>
+        <v>-33896326.522721097</v>
       </c>
       <c r="M5">
-        <v>2357136815.846096</v>
+        <v>3974673369.7583289</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>17</v>
       </c>
       <c r="B6">
-        <v>6494.644935378301</v>
+        <v>13489.438525424701</v>
       </c>
       <c r="C6">
-        <v>-169.2346162776211</v>
+        <v>9828.7060590990714</v>
       </c>
       <c r="D6">
-        <v>12160.73353396925</v>
+        <v>16781.060391310992</v>
       </c>
       <c r="E6">
-        <v>2091.204030004019</v>
+        <v>20690.252805414861</v>
       </c>
       <c r="F6">
-        <v>-42.47659965253237</v>
+        <v>12097.69253502273</v>
       </c>
       <c r="G6">
-        <v>4980.793696439016</v>
+        <v>29277.591524930289</v>
       </c>
       <c r="H6">
-        <v>488403793.7853814</v>
+        <v>227148655.32962629</v>
       </c>
       <c r="I6">
-        <v>-12726612.37869336</v>
+        <v>165505581.32916951</v>
       </c>
       <c r="J6">
-        <v>914499322.4880207</v>
+        <v>282576275.92928439</v>
       </c>
       <c r="K6">
-        <v>278130135.9905345</v>
+        <v>2751803623.1201768</v>
       </c>
       <c r="L6">
-        <v>-5649387.753786805</v>
+        <v>1608993107.1580231</v>
       </c>
       <c r="M6">
-        <v>662445561.626389</v>
+        <v>3893919672.8157282</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
       </c>
       <c r="B7">
-        <v>13489.4385254247</v>
+        <v>152108.7678282618</v>
       </c>
       <c r="C7">
-        <v>9828.706059099071</v>
+        <v>112504.7828238988</v>
       </c>
       <c r="D7">
-        <v>16781.06039131099</v>
+        <v>184478.67291604119</v>
       </c>
       <c r="E7">
-        <v>3448.375467569117</v>
+        <v>431489.76153525012</v>
       </c>
       <c r="F7">
-        <v>2016.282089170447</v>
+        <v>197362.18031268951</v>
       </c>
       <c r="G7">
-        <v>4879.598587488372</v>
+        <v>799755.80277953483</v>
       </c>
       <c r="H7">
-        <v>227148655.3296263</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>165505581.3291695</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>282576275.9292844</v>
+        <v>0</v>
       </c>
       <c r="K7">
-        <v>458633937.1866926</v>
+        <v>57388138284.188263</v>
       </c>
       <c r="L7">
-        <v>268165517.8596694</v>
+        <v>26249169981.5877</v>
       </c>
       <c r="M7">
-        <v>648986612.1359534</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>152108.7678282618</v>
-      </c>
-      <c r="C8">
-        <v>112504.7828238988</v>
-      </c>
-      <c r="D8">
-        <v>184478.6729160412</v>
-      </c>
-      <c r="E8">
-        <v>143829.9205117502</v>
-      </c>
-      <c r="F8">
-        <v>65787.39343756315</v>
-      </c>
-      <c r="G8">
-        <v>266585.2675931788</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>19129379428.06278</v>
-      </c>
-      <c r="L8">
-        <v>8749723327.1959</v>
-      </c>
-      <c r="M8">
-        <v>35455840589.89278</v>
+        <v>106367521769.6781</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/cases_prev_2019.xlsx
+++ b/output/Tables/2019/cases_prev_2019.xlsx
@@ -1,89 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/2019/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E11EAC3-8B5D-7647-84DA-7477D18880B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34040" yWindow="-940" windowWidth="19980" windowHeight="10440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
-  <si>
-    <t>disease</t>
-  </si>
-  <si>
-    <t>tot_cases_mid</t>
-  </si>
-  <si>
-    <t>tot_cases_low</t>
-  </si>
-  <si>
-    <t>tot_cases_up</t>
-  </si>
-  <si>
-    <t>tot_daly_mid</t>
-  </si>
-  <si>
-    <t>tot_daly_low</t>
-  </si>
-  <si>
-    <t>tot_daly_up</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_mid</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_low</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_up</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_mid</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_low</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_up</t>
-  </si>
-  <si>
-    <t>mort</t>
-  </si>
-  <si>
-    <t>cvd</t>
-  </si>
-  <si>
-    <t>cancer</t>
-  </si>
-  <si>
-    <t>diab2</t>
-  </si>
-  <si>
-    <t>dem</t>
-  </si>
-  <si>
-    <t>dep</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -183,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -217,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -252,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -428,85 +350,100 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_mid</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_low</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_up</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_mid</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_up</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_mid</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_up</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_mid</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_up</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>13</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
       </c>
       <c r="B2">
-        <v>58808.728546195358</v>
+        <v>174330.6445862389</v>
       </c>
       <c r="C2">
-        <v>50683.178351604387</v>
+        <v>116208.9023148201</v>
       </c>
       <c r="D2">
-        <v>66422.72611868204</v>
+        <v>227736.9798202114</v>
       </c>
       <c r="E2">
-        <v>608073.21169749764</v>
+        <v>1823005.99859463</v>
       </c>
       <c r="F2">
-        <v>524476.11935019644</v>
+        <v>1213282.007248004</v>
       </c>
       <c r="G2">
-        <v>686442.77472859167</v>
+        <v>2381535.474298258</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -518,200 +455,210 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>80873737155.767181</v>
+        <v>242459797813.0858</v>
       </c>
       <c r="L2">
-        <v>69755323873.576126</v>
+        <v>161366506963.9846</v>
       </c>
       <c r="M2">
-        <v>91296889038.902695</v>
+        <v>316744218081.6683</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>14</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
       </c>
       <c r="B3">
-        <v>39658.266804171319</v>
+        <v>252922.4563998251</v>
       </c>
       <c r="C3">
-        <v>25131.726867947789</v>
+        <v>168306.9396435622</v>
       </c>
       <c r="D3">
-        <v>53975.068716545167</v>
+        <v>330442.626077514</v>
       </c>
       <c r="E3">
-        <v>34277.266819580909</v>
+        <v>218259.6145996814</v>
       </c>
       <c r="F3">
-        <v>17053.605445734069</v>
+        <v>113889.1137873751</v>
       </c>
       <c r="G3">
-        <v>56813.856312378193</v>
+        <v>347631.7082758007</v>
       </c>
       <c r="H3">
-        <v>2209044777.5259452</v>
+        <v>14088286666.38304</v>
       </c>
       <c r="I3">
-        <v>1399887449.998425</v>
+        <v>9375033152.025738</v>
       </c>
       <c r="J3">
-        <v>3006519277.649013</v>
+        <v>18406315157.76973</v>
       </c>
       <c r="K3">
-        <v>4558876487.004261</v>
+        <v>29028528741.75763</v>
       </c>
       <c r="L3">
-        <v>2268129524.28263</v>
+        <v>15147252133.72089</v>
       </c>
       <c r="M3">
-        <v>7556242889.5462999</v>
+        <v>46235017200.68149</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>15</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
       </c>
       <c r="B4">
-        <v>30550.639890961549</v>
+        <v>762164.1878813909</v>
       </c>
       <c r="C4">
-        <v>1406.091732024955</v>
+        <v>507054.4315154804</v>
       </c>
       <c r="D4">
-        <v>61810.714848468713</v>
+        <v>995835.6412512294</v>
       </c>
       <c r="E4">
-        <v>45507.349760629091</v>
+        <v>1139967.134016047</v>
       </c>
       <c r="F4">
-        <v>1705.4218396054689</v>
+        <v>599961.2402660514</v>
       </c>
       <c r="G4">
-        <v>106336.9992111021</v>
+        <v>1720278.099028435</v>
       </c>
       <c r="H4">
-        <v>452363324.86546648</v>
+        <v>11285365129.95992</v>
       </c>
       <c r="I4">
-        <v>20820000.27609352</v>
+        <v>7507954967.44974</v>
       </c>
       <c r="J4">
-        <v>915231254.76127458</v>
+        <v>14745338340.00703</v>
       </c>
       <c r="K4">
-        <v>6052477518.1636696</v>
+        <v>151615628824.1342</v>
       </c>
       <c r="L4">
-        <v>226821104.66752741</v>
+        <v>79794844955.38483</v>
       </c>
       <c r="M4">
-        <v>14142820895.07658</v>
+        <v>228796987170.7818</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>16</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
       </c>
       <c r="B5">
-        <v>6494.6449353783009</v>
+        <v>72503.57934043859</v>
       </c>
       <c r="C5">
-        <v>-169.23461627762109</v>
+        <v>48242.19250276188</v>
       </c>
       <c r="D5">
-        <v>12160.733533969251</v>
+        <v>94718.537063378</v>
       </c>
       <c r="E5">
-        <v>12547.224180024181</v>
+        <v>141291.4731544685</v>
       </c>
       <c r="F5">
-        <v>-254.85959791519619</v>
+        <v>69996.87793557833</v>
       </c>
       <c r="G5">
-        <v>29884.76217863405</v>
+        <v>234396.4727826468</v>
       </c>
       <c r="H5">
-        <v>488403793.78538138</v>
+        <v>5452341669.980335</v>
       </c>
       <c r="I5">
-        <v>-12726612.378693361</v>
+        <v>3627861118.400247</v>
       </c>
       <c r="J5">
-        <v>914499322.48802066</v>
+        <v>7122928705.703065</v>
       </c>
       <c r="K5">
-        <v>1668780815.9432149</v>
+        <v>18791765929.54431</v>
       </c>
       <c r="L5">
-        <v>-33896326.522721097</v>
+        <v>9309584765.431919</v>
       </c>
       <c r="M5">
-        <v>3974673369.7583289</v>
+        <v>31174730880.09203</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>17</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
       </c>
       <c r="B6">
-        <v>13489.438525424701</v>
+        <v>56757.81406590881</v>
       </c>
       <c r="C6">
-        <v>9828.7060590990714</v>
+        <v>37789.16740043839</v>
       </c>
       <c r="D6">
-        <v>16781.060391310992</v>
+        <v>74214.63675740108</v>
       </c>
       <c r="E6">
-        <v>20690.252805414861</v>
+        <v>86767.87394769686</v>
       </c>
       <c r="F6">
-        <v>12097.69253502273</v>
+        <v>46206.61736684766</v>
       </c>
       <c r="G6">
-        <v>29277.591524930289</v>
+        <v>129219.1434959386</v>
       </c>
       <c r="H6">
-        <v>227148655.32962629</v>
+        <v>955744831.0558244</v>
       </c>
       <c r="I6">
-        <v>165505581.32916951</v>
+        <v>636331789.8559825</v>
       </c>
       <c r="J6">
-        <v>282576275.92928439</v>
+        <v>1249700268.357857</v>
       </c>
       <c r="K6">
-        <v>2751803623.1201768</v>
+        <v>11540127235.04368</v>
       </c>
       <c r="L6">
-        <v>1608993107.1580231</v>
+        <v>6145480109.790739</v>
       </c>
       <c r="M6">
-        <v>3893919672.8157282</v>
+        <v>17186146084.95983</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>18</v>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
       </c>
       <c r="B7">
-        <v>152108.7678282618</v>
+        <v>1073732.992683997</v>
       </c>
       <c r="C7">
-        <v>112504.7828238988</v>
+        <v>714283.0059942366</v>
       </c>
       <c r="D7">
-        <v>184478.67291604119</v>
+        <v>1403514.556590366</v>
       </c>
       <c r="E7">
-        <v>431489.76153525012</v>
+        <v>3050506.300033989</v>
       </c>
       <c r="F7">
-        <v>197362.18031268951</v>
+        <v>1255249.305934041</v>
       </c>
       <c r="G7">
-        <v>799755.80277953483</v>
+        <v>6093762.271773634</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -723,13 +670,13 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>57388138284.188263</v>
+        <v>405717337904.5205</v>
       </c>
       <c r="L7">
-        <v>26249169981.5877</v>
+        <v>166948157689.2274</v>
       </c>
       <c r="M7">
-        <v>106367521769.6781</v>
+        <v>810470382145.8934</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/cases_prev_2019.xlsx
+++ b/output/Tables/2019/cases_prev_2019.xlsx
@@ -1,21 +1,89 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/2019/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519D44AA-B2A7-454E-A5EC-BE24FB3051D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>tot_cases_mid</t>
+  </si>
+  <si>
+    <t>tot_cases_low</t>
+  </si>
+  <si>
+    <t>tot_cases_up</t>
+  </si>
+  <si>
+    <t>tot_daly_mid</t>
+  </si>
+  <si>
+    <t>tot_daly_low</t>
+  </si>
+  <si>
+    <t>tot_daly_up</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_mid</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_low</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_up</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_mid</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_up</t>
+  </si>
+  <si>
+    <t>mort</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>cancer</t>
+  </si>
+  <si>
+    <t>diab2</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>dep</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +131,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +183,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +217,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +252,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,91 +428,72 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_mid</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_up</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_mid</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_up</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_mid</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_low</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_up</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_mid</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_up</t>
-        </is>
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>13</v>
       </c>
       <c r="B2">
-        <v>174330.6445862389</v>
+        <v>174330.64458623889</v>
       </c>
       <c r="C2">
-        <v>116208.9023148201</v>
+        <v>116208.90231482009</v>
       </c>
       <c r="D2">
-        <v>227736.9798202114</v>
+        <v>227736.97982021139</v>
       </c>
       <c r="E2">
         <v>1823005.99859463</v>
@@ -443,7 +502,7 @@
         <v>1213282.007248004</v>
       </c>
       <c r="G2">
-        <v>2381535.474298258</v>
+        <v>2381535.4742982578</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -455,29 +514,27 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>242459797813.0858</v>
+        <v>242459797813.08578</v>
       </c>
       <c r="L2">
-        <v>161366506963.9846</v>
+        <v>161366506963.98459</v>
       </c>
       <c r="M2">
-        <v>316744218081.6683</v>
+        <v>316744218081.66827</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
       </c>
       <c r="B3">
-        <v>252922.4563998251</v>
+        <v>252922.45639982511</v>
       </c>
       <c r="C3">
-        <v>168306.9396435622</v>
+        <v>168306.93964356219</v>
       </c>
       <c r="D3">
-        <v>330442.626077514</v>
+        <v>330442.62607751403</v>
       </c>
       <c r="E3">
         <v>218259.6145996814</v>
@@ -486,133 +543,127 @@
         <v>113889.1137873751</v>
       </c>
       <c r="G3">
-        <v>347631.7082758007</v>
+        <v>347631.70827580069</v>
       </c>
       <c r="H3">
-        <v>14088286666.38304</v>
+        <v>14088286666.383039</v>
       </c>
       <c r="I3">
-        <v>9375033152.025738</v>
+        <v>9375033152.0257378</v>
       </c>
       <c r="J3">
         <v>18406315157.76973</v>
       </c>
       <c r="K3">
-        <v>29028528741.75763</v>
+        <v>29028528741.757629</v>
       </c>
       <c r="L3">
         <v>15147252133.72089</v>
       </c>
       <c r="M3">
-        <v>46235017200.68149</v>
+        <v>46235017200.681488</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>15</v>
       </c>
       <c r="B4">
-        <v>762164.1878813909</v>
+        <v>762164.18788139091</v>
       </c>
       <c r="C4">
-        <v>507054.4315154804</v>
+        <v>507054.43151548039</v>
       </c>
       <c r="D4">
-        <v>995835.6412512294</v>
+        <v>995835.64125122945</v>
       </c>
       <c r="E4">
         <v>1139967.134016047</v>
       </c>
       <c r="F4">
-        <v>599961.2402660514</v>
+        <v>599961.24026605138</v>
       </c>
       <c r="G4">
-        <v>1720278.099028435</v>
+        <v>1720278.0990284351</v>
       </c>
       <c r="H4">
-        <v>11285365129.95992</v>
+        <v>11285365129.959921</v>
       </c>
       <c r="I4">
-        <v>7507954967.44974</v>
+        <v>7507954967.4497404</v>
       </c>
       <c r="J4">
         <v>14745338340.00703</v>
       </c>
       <c r="K4">
-        <v>151615628824.1342</v>
+        <v>151615628824.13419</v>
       </c>
       <c r="L4">
-        <v>79794844955.38483</v>
+        <v>79794844955.384827</v>
       </c>
       <c r="M4">
         <v>228796987170.7818</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>16</v>
       </c>
       <c r="B5">
-        <v>72503.57934043859</v>
+        <v>72503.579340438591</v>
       </c>
       <c r="C5">
-        <v>48242.19250276188</v>
+        <v>48242.192502761878</v>
       </c>
       <c r="D5">
-        <v>94718.537063378</v>
+        <v>94718.537063377997</v>
       </c>
       <c r="E5">
-        <v>141291.4731544685</v>
+        <v>141291.47315446849</v>
       </c>
       <c r="F5">
-        <v>69996.87793557833</v>
+        <v>69996.877935578334</v>
       </c>
       <c r="G5">
         <v>234396.4727826468</v>
       </c>
       <c r="H5">
-        <v>5452341669.980335</v>
+        <v>5452341669.9803352</v>
       </c>
       <c r="I5">
-        <v>3627861118.400247</v>
+        <v>3627861118.4002471</v>
       </c>
       <c r="J5">
-        <v>7122928705.703065</v>
+        <v>7122928705.7030649</v>
       </c>
       <c r="K5">
-        <v>18791765929.54431</v>
+        <v>18791765929.544312</v>
       </c>
       <c r="L5">
-        <v>9309584765.431919</v>
+        <v>9309584765.4319191</v>
       </c>
       <c r="M5">
         <v>31174730880.09203</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>17</v>
       </c>
       <c r="B6">
-        <v>56757.81406590881</v>
+        <v>56757.814065908809</v>
       </c>
       <c r="C6">
-        <v>37789.16740043839</v>
+        <v>37789.167400438389</v>
       </c>
       <c r="D6">
         <v>74214.63675740108</v>
       </c>
       <c r="E6">
-        <v>86767.87394769686</v>
+        <v>86767.873947696862</v>
       </c>
       <c r="F6">
-        <v>46206.61736684766</v>
+        <v>46206.617366847662</v>
       </c>
       <c r="G6">
         <v>129219.1434959386</v>
@@ -621,7 +672,7 @@
         <v>955744831.0558244</v>
       </c>
       <c r="I6">
-        <v>636331789.8559825</v>
+        <v>636331789.85598254</v>
       </c>
       <c r="J6">
         <v>1249700268.357857</v>
@@ -630,35 +681,33 @@
         <v>11540127235.04368</v>
       </c>
       <c r="L6">
-        <v>6145480109.790739</v>
+        <v>6145480109.7907391</v>
       </c>
       <c r="M6">
-        <v>17186146084.95983</v>
+        <v>17186146084.959831</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
       </c>
       <c r="B7">
-        <v>1073732.992683997</v>
+        <v>1073732.9926839969</v>
       </c>
       <c r="C7">
-        <v>714283.0059942366</v>
+        <v>714283.00599423656</v>
       </c>
       <c r="D7">
-        <v>1403514.556590366</v>
+        <v>1403514.5565903659</v>
       </c>
       <c r="E7">
-        <v>3050506.300033989</v>
+        <v>3050506.3000339889</v>
       </c>
       <c r="F7">
         <v>1255249.305934041</v>
       </c>
       <c r="G7">
-        <v>6093762.271773634</v>
+        <v>6093762.2717736335</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -670,13 +719,13 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>405717337904.5205</v>
+        <v>405717337904.52051</v>
       </c>
       <c r="L7">
-        <v>166948157689.2274</v>
+        <v>166948157689.22739</v>
       </c>
       <c r="M7">
-        <v>810470382145.8934</v>
+        <v>810470382145.89343</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/2019/cases_prev_2019.xlsx
+++ b/output/Tables/2019/cases_prev_2019.xlsx
@@ -1,89 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/2019/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{519D44AA-B2A7-454E-A5EC-BE24FB3051D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
-  <si>
-    <t>disease</t>
-  </si>
-  <si>
-    <t>tot_cases_mid</t>
-  </si>
-  <si>
-    <t>tot_cases_low</t>
-  </si>
-  <si>
-    <t>tot_cases_up</t>
-  </si>
-  <si>
-    <t>tot_daly_mid</t>
-  </si>
-  <si>
-    <t>tot_daly_low</t>
-  </si>
-  <si>
-    <t>tot_daly_up</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_mid</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_low</t>
-  </si>
-  <si>
-    <t>tot_medic_costs_up</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_mid</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_low</t>
-  </si>
-  <si>
-    <t>tot_soc_costs_up</t>
-  </si>
-  <si>
-    <t>mort</t>
-  </si>
-  <si>
-    <t>cvd</t>
-  </si>
-  <si>
-    <t>cancer</t>
-  </si>
-  <si>
-    <t>diab2</t>
-  </si>
-  <si>
-    <t>dem</t>
-  </si>
-  <si>
-    <t>dep</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -183,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -217,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -252,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -428,72 +350,91 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_mid</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_low</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tot_cases_up</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_mid</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_up</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_mid</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_up</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_mid</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_up</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>13</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
       </c>
       <c r="B2">
-        <v>174330.64458623889</v>
+        <v>174330.6445862389</v>
       </c>
       <c r="C2">
-        <v>116208.90231482009</v>
+        <v>116208.9023148201</v>
       </c>
       <c r="D2">
-        <v>227736.97982021139</v>
+        <v>227736.9798202114</v>
       </c>
       <c r="E2">
         <v>1823005.99859463</v>
@@ -502,7 +443,7 @@
         <v>1213282.007248004</v>
       </c>
       <c r="G2">
-        <v>2381535.4742982578</v>
+        <v>2381535.474298258</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -514,156 +455,164 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>242459797813.08578</v>
+        <v>242459797813.0858</v>
       </c>
       <c r="L2">
-        <v>161366506963.98459</v>
+        <v>161366506963.9846</v>
       </c>
       <c r="M2">
-        <v>316744218081.66827</v>
+        <v>316744218081.6683</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>14</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
       </c>
       <c r="B3">
-        <v>252922.45639982511</v>
+        <v>762164.1878813909</v>
       </c>
       <c r="C3">
-        <v>168306.93964356219</v>
+        <v>507054.4315154804</v>
       </c>
       <c r="D3">
-        <v>330442.62607751403</v>
+        <v>995835.6412512294</v>
       </c>
       <c r="E3">
+        <v>1139967.134016047</v>
+      </c>
+      <c r="F3">
+        <v>599961.2402660514</v>
+      </c>
+      <c r="G3">
+        <v>1720278.099028435</v>
+      </c>
+      <c r="H3">
+        <v>11285365129.95992</v>
+      </c>
+      <c r="I3">
+        <v>7507954967.44974</v>
+      </c>
+      <c r="J3">
+        <v>14745338340.00703</v>
+      </c>
+      <c r="K3">
+        <v>151615628824.1342</v>
+      </c>
+      <c r="L3">
+        <v>79794844955.38483</v>
+      </c>
+      <c r="M3">
+        <v>228796987170.7818</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>252922.4563998251</v>
+      </c>
+      <c r="C4">
+        <v>168306.9396435622</v>
+      </c>
+      <c r="D4">
+        <v>330442.626077514</v>
+      </c>
+      <c r="E4">
         <v>218259.6145996814</v>
       </c>
-      <c r="F3">
+      <c r="F4">
         <v>113889.1137873751</v>
       </c>
-      <c r="G3">
-        <v>347631.70827580069</v>
-      </c>
-      <c r="H3">
-        <v>14088286666.383039</v>
-      </c>
-      <c r="I3">
-        <v>9375033152.0257378</v>
-      </c>
-      <c r="J3">
+      <c r="G4">
+        <v>347631.7082758007</v>
+      </c>
+      <c r="H4">
+        <v>14088286666.38304</v>
+      </c>
+      <c r="I4">
+        <v>9375033152.025738</v>
+      </c>
+      <c r="J4">
         <v>18406315157.76973</v>
       </c>
-      <c r="K3">
-        <v>29028528741.757629</v>
-      </c>
-      <c r="L3">
+      <c r="K4">
+        <v>29028528741.75763</v>
+      </c>
+      <c r="L4">
         <v>15147252133.72089</v>
       </c>
-      <c r="M3">
-        <v>46235017200.681488</v>
+      <c r="M4">
+        <v>46235017200.68149</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4">
-        <v>762164.18788139091</v>
-      </c>
-      <c r="C4">
-        <v>507054.43151548039</v>
-      </c>
-      <c r="D4">
-        <v>995835.64125122945</v>
-      </c>
-      <c r="E4">
-        <v>1139967.134016047</v>
-      </c>
-      <c r="F4">
-        <v>599961.24026605138</v>
-      </c>
-      <c r="G4">
-        <v>1720278.0990284351</v>
-      </c>
-      <c r="H4">
-        <v>11285365129.959921</v>
-      </c>
-      <c r="I4">
-        <v>7507954967.4497404</v>
-      </c>
-      <c r="J4">
-        <v>14745338340.00703</v>
-      </c>
-      <c r="K4">
-        <v>151615628824.13419</v>
-      </c>
-      <c r="L4">
-        <v>79794844955.384827</v>
-      </c>
-      <c r="M4">
-        <v>228796987170.7818</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>16</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
       </c>
       <c r="B5">
-        <v>72503.579340438591</v>
+        <v>72503.57934043859</v>
       </c>
       <c r="C5">
-        <v>48242.192502761878</v>
+        <v>48242.19250276188</v>
       </c>
       <c r="D5">
-        <v>94718.537063377997</v>
+        <v>94718.537063378</v>
       </c>
       <c r="E5">
-        <v>141291.47315446849</v>
+        <v>141291.4731544685</v>
       </c>
       <c r="F5">
-        <v>69996.877935578334</v>
+        <v>69996.87793557833</v>
       </c>
       <c r="G5">
         <v>234396.4727826468</v>
       </c>
       <c r="H5">
-        <v>5452341669.9803352</v>
+        <v>5452341669.980335</v>
       </c>
       <c r="I5">
-        <v>3627861118.4002471</v>
+        <v>3627861118.400247</v>
       </c>
       <c r="J5">
-        <v>7122928705.7030649</v>
+        <v>7122928705.703065</v>
       </c>
       <c r="K5">
-        <v>18791765929.544312</v>
+        <v>18791765929.54431</v>
       </c>
       <c r="L5">
-        <v>9309584765.4319191</v>
+        <v>9309584765.431919</v>
       </c>
       <c r="M5">
         <v>31174730880.09203</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>17</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
       </c>
       <c r="B6">
-        <v>56757.814065908809</v>
+        <v>56757.81406590881</v>
       </c>
       <c r="C6">
-        <v>37789.167400438389</v>
+        <v>37789.16740043839</v>
       </c>
       <c r="D6">
         <v>74214.63675740108</v>
       </c>
       <c r="E6">
-        <v>86767.873947696862</v>
+        <v>86767.87394769686</v>
       </c>
       <c r="F6">
-        <v>46206.617366847662</v>
+        <v>46206.61736684766</v>
       </c>
       <c r="G6">
         <v>129219.1434959386</v>
@@ -672,7 +621,7 @@
         <v>955744831.0558244</v>
       </c>
       <c r="I6">
-        <v>636331789.85598254</v>
+        <v>636331789.8559825</v>
       </c>
       <c r="J6">
         <v>1249700268.357857</v>
@@ -681,33 +630,35 @@
         <v>11540127235.04368</v>
       </c>
       <c r="L6">
-        <v>6145480109.7907391</v>
+        <v>6145480109.790739</v>
       </c>
       <c r="M6">
-        <v>17186146084.959831</v>
+        <v>17186146084.95983</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>18</v>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
       </c>
       <c r="B7">
-        <v>1073732.9926839969</v>
+        <v>1073732.992683997</v>
       </c>
       <c r="C7">
-        <v>714283.00599423656</v>
+        <v>714283.0059942366</v>
       </c>
       <c r="D7">
-        <v>1403514.5565903659</v>
+        <v>1403514.556590366</v>
       </c>
       <c r="E7">
-        <v>3050506.3000339889</v>
+        <v>3050506.300033989</v>
       </c>
       <c r="F7">
         <v>1255249.305934041</v>
       </c>
       <c r="G7">
-        <v>6093762.2717736335</v>
+        <v>6093762.271773634</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -719,13 +670,13 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>405717337904.52051</v>
+        <v>405717337904.5205</v>
       </c>
       <c r="L7">
-        <v>166948157689.22739</v>
+        <v>166948157689.2274</v>
       </c>
       <c r="M7">
-        <v>810470382145.89343</v>
+        <v>810470382145.8934</v>
       </c>
     </row>
   </sheetData>
